--- a/漢字（かんじ）/s.xlsx
+++ b/漢字（かんじ）/s.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="529">
   <si>
     <t>仮名</t>
   </si>
@@ -990,6 +990,12 @@
 進歩｜しんぽ
 進度｜しんど
 進学｜しんがく</t>
+  </si>
+  <si>
+    <t>振</t>
+  </si>
+  <si>
+    <t>振動｜しんどう</t>
   </si>
   <si>
     <t>診</t>
@@ -3556,7 +3562,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -4241,25 +4247,25 @@
         <v>223</v>
       </c>
     </row>
-    <row r="37" ht="36" spans="1:3">
+    <row r="37" spans="1:3">
       <c r="A37" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" ht="36" spans="1:3">
       <c r="A38" s="1" t="s">
         <v>192</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="2" t="s">
         <v>227</v>
       </c>
     </row>
@@ -4274,42 +4280,42 @@
         <v>229</v>
       </c>
     </row>
-    <row r="40" ht="36" spans="1:3">
+    <row r="40" spans="1:3">
       <c r="A40" s="1" t="s">
         <v>192</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="1" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" ht="36" spans="1:3">
       <c r="A41" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="C41" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="1" t="s">
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="1" t="s">
         <v>234</v>
-      </c>
-    </row>
-    <row r="42" ht="54" spans="1:3">
-      <c r="A42" s="1" t="s">
-        <v>232</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="1" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="43" ht="54" spans="1:3">
       <c r="A43" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>237</v>
@@ -4318,31 +4324,31 @@
         <v>238</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" ht="54" spans="1:3">
       <c r="A44" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="2" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="45" ht="126" spans="1:3">
+    <row r="45" spans="1:3">
       <c r="A45" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="1" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" ht="126" spans="1:3">
       <c r="A46" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>243</v>
@@ -4353,7 +4359,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>245</v>
@@ -4364,7 +4370,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>247</v>
@@ -4375,7 +4381,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>249</v>
@@ -4384,20 +4390,20 @@
         <v>250</v>
       </c>
     </row>
-    <row r="50" ht="52.2" customHeight="1" spans="1:3">
+    <row r="50" spans="1:3">
       <c r="A50" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="C50" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C50" s="2" t="s">
+    </row>
+    <row r="51" ht="52.2" customHeight="1" spans="1:3">
+      <c r="A51" s="1" t="s">
         <v>253</v>
-      </c>
-    </row>
-    <row r="51" ht="54" spans="1:3">
-      <c r="A51" s="1" t="s">
-        <v>251</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>254</v>
@@ -4406,9 +4412,9 @@
         <v>255</v>
       </c>
     </row>
-    <row r="52" ht="90" spans="1:3">
+    <row r="52" ht="54" spans="1:3">
       <c r="A52" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>256</v>
@@ -4417,9 +4423,9 @@
         <v>257</v>
       </c>
     </row>
-    <row r="53" ht="180" spans="1:3">
+    <row r="53" ht="90" spans="1:3">
       <c r="A53" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>258</v>
@@ -4428,9 +4434,9 @@
         <v>259</v>
       </c>
     </row>
-    <row r="54" ht="72" spans="1:3">
+    <row r="54" ht="180" spans="1:3">
       <c r="A54" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>260</v>
@@ -4439,9 +4445,9 @@
         <v>261</v>
       </c>
     </row>
-    <row r="55" ht="36" spans="1:3">
+    <row r="55" ht="72" spans="1:3">
       <c r="A55" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>262</v>
@@ -4452,7 +4458,7 @@
     </row>
     <row r="56" ht="36" spans="1:3">
       <c r="A56" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>264</v>
@@ -4463,7 +4469,7 @@
     </row>
     <row r="57" ht="36" spans="1:3">
       <c r="A57" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>266</v>
@@ -4472,9 +4478,9 @@
         <v>267</v>
       </c>
     </row>
-    <row r="58" ht="90" spans="1:3">
+    <row r="58" ht="36" spans="1:3">
       <c r="A58" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>268</v>
@@ -4483,31 +4489,31 @@
         <v>269</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" ht="90" spans="1:3">
       <c r="A59" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="2" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="1" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="61" ht="36" spans="1:3">
+    <row r="61" spans="1:3">
       <c r="A61" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>274</v>
@@ -4518,29 +4524,29 @@
     </row>
     <row r="62" ht="36" spans="1:3">
       <c r="A62" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="63" ht="54" spans="1:3">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="63" ht="36" spans="1:3">
       <c r="A63" s="1" t="s">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="C63" s="2" t="s">
+    </row>
+    <row r="64" ht="54" spans="1:3">
+      <c r="A64" s="1" t="s">
         <v>279</v>
-      </c>
-    </row>
-    <row r="64" ht="108" spans="1:3">
-      <c r="A64" s="1" t="s">
-        <v>277</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>280</v>
@@ -4549,9 +4555,9 @@
         <v>281</v>
       </c>
     </row>
-    <row r="65" ht="36" spans="1:3">
+    <row r="65" ht="108" spans="1:3">
       <c r="A65" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>282</v>
@@ -4562,7 +4568,7 @@
     </row>
     <row r="66" ht="36" spans="1:3">
       <c r="A66" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>284</v>
@@ -4571,20 +4577,20 @@
         <v>285</v>
       </c>
     </row>
-    <row r="67" ht="90" spans="1:3">
+    <row r="67" ht="36" spans="1:3">
       <c r="A67" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="C67" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C67" s="2" t="s">
+    </row>
+    <row r="68" ht="90" spans="1:3">
+      <c r="A68" s="1" t="s">
         <v>288</v>
-      </c>
-    </row>
-    <row r="68" ht="36" spans="1:3">
-      <c r="A68" s="1" t="s">
-        <v>286</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>289</v>
@@ -4595,7 +4601,7 @@
     </row>
     <row r="69" ht="36" spans="1:3">
       <c r="A69" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>291</v>
@@ -4604,31 +4610,31 @@
         <v>292</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
+    <row r="70" ht="36" spans="1:3">
       <c r="A70" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="2" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="71" ht="36" spans="1:3">
+    <row r="71" spans="1:3">
       <c r="A71" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="72" ht="54" spans="1:3">
+    <row r="72" ht="36" spans="1:3">
       <c r="A72" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>297</v>
@@ -4637,9 +4643,9 @@
         <v>298</v>
       </c>
     </row>
-    <row r="73" ht="72" spans="1:3">
+    <row r="73" ht="54" spans="1:3">
       <c r="A73" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>299</v>
@@ -4648,50 +4654,50 @@
         <v>300</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
+    <row r="74" ht="72" spans="1:3">
       <c r="A74" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="2" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="75" ht="72" spans="1:3">
+    <row r="75" spans="1:3">
       <c r="A75" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C75" s="1" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" ht="72" spans="1:3">
       <c r="A76" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="77" ht="36" spans="1:3">
+      <c r="C76" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
       <c r="A77" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C77" s="2" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="78" ht="72" spans="1:3">
+    <row r="78" ht="36" spans="1:3">
       <c r="A78" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>308</v>
@@ -4700,20 +4706,20 @@
         <v>309</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" ht="72" spans="1:3">
       <c r="A79" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" s="2" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>312</v>
@@ -4722,42 +4728,42 @@
         <v>313</v>
       </c>
     </row>
-    <row r="81" ht="54" spans="1:3">
+    <row r="81" spans="1:3">
       <c r="A81" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C81" s="1" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" ht="54" spans="1:3">
       <c r="A82" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" s="2" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="83" ht="72" spans="1:3">
+    <row r="83" spans="1:3">
       <c r="A83" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="C83" s="1" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="84" ht="36" spans="1:3">
+    <row r="84" ht="72" spans="1:3">
       <c r="A84" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>320</v>
@@ -4768,7 +4774,7 @@
     </row>
     <row r="85" ht="36" spans="1:3">
       <c r="A85" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>322</v>
@@ -4777,9 +4783,9 @@
         <v>323</v>
       </c>
     </row>
-    <row r="86" ht="72" spans="1:3">
+    <row r="86" ht="36" spans="1:3">
       <c r="A86" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>324</v>
@@ -4788,42 +4794,42 @@
         <v>325</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" ht="72" spans="1:3">
       <c r="A87" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C87" s="2" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="88" ht="90" spans="1:3">
+    <row r="88" spans="1:3">
       <c r="A88" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C88" s="1" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" ht="90" spans="1:3">
       <c r="A89" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C89" s="2" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>332</v>
@@ -4832,59 +4838,70 @@
         <v>333</v>
       </c>
     </row>
-    <row r="91" ht="36" spans="1:3">
+    <row r="91" spans="1:3">
       <c r="A91" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="C91" s="2" t="s">
+      <c r="C91" s="1" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" ht="36" spans="1:3">
       <c r="A92" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C92" s="2" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>338</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="94" ht="54" spans="1:3">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
       <c r="A94" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="C94" s="2" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="95" spans="1:3">
+      <c r="C94" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="95" ht="54" spans="1:3">
       <c r="A95" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C95" s="2" t="s">
         <v>342</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -4915,167 +4932,167 @@
     </row>
     <row r="2" ht="18" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" ht="36" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D4" s="1"/>
     </row>
     <row r="5" ht="18" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" ht="56.4" customHeight="1" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="8" ht="36" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9" ht="78.6" customHeight="1" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10" ht="18.6" customHeight="1" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C11" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12" ht="27.6" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C15" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16" ht="15.6" spans="1:4">
       <c r="A16" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>157</v>
@@ -5122,373 +5139,373 @@
     </row>
     <row r="2" ht="67.2" customHeight="1" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" ht="36" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" ht="36" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" ht="58.2" customHeight="1" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="6" ht="37.8" customHeight="1" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="7" ht="54" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8" ht="91.2" customHeight="1" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9" ht="126" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="10" ht="36" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11" ht="57" customHeight="1" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="12" ht="108" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="14" ht="72" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="15" ht="90" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="16" ht="180" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="18" ht="36" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="19" ht="36" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="20" ht="162" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="21" ht="36" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="22" ht="126" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="24" ht="54" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>158</v>
@@ -5496,57 +5513,57 @@
     </row>
     <row r="27" ht="36" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="28" ht="54" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="29" ht="54" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="30" ht="90" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="31" ht="36" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
   </sheetData>
@@ -5581,305 +5598,305 @@
     </row>
     <row r="2" ht="54" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="4" ht="54" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="5" ht="54" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" ht="36" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="7" ht="130.2" customHeight="1" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8" ht="144" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9" ht="36" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="10" ht="144" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="11" ht="72" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="13" ht="72" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="16" ht="36.6" customHeight="1" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="18" ht="36" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="19" ht="36" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>

--- a/漢字（かんじ）/s.xlsx
+++ b/漢字（かんじ）/s.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="3"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="さ" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="533">
   <si>
     <t>仮名</t>
   </si>
@@ -72,6 +72,7 @@
   </si>
   <si>
     <t>差額｜さがく
+格差｜かくさ
 偏差｜へんさ
 偏差値｜へんさち</t>
   </si>
@@ -325,6 +326,13 @@
   </si>
   <si>
     <t>賛成｜さんせい</t>
+  </si>
+  <si>
+    <t>散</t>
+  </si>
+  <si>
+    <t>拡散｜かくさん
+拡散希望｜かくさんきぼう</t>
   </si>
   <si>
     <t>し</t>
@@ -431,7 +439,8 @@
   </si>
   <si>
     <t>試行｜しこう
-試合｜しあい</t>
+試合｜しあい
+試乗｜しじょう</t>
   </si>
   <si>
     <t>社</t>
@@ -500,7 +509,10 @@
   </si>
   <si>
     <t>資料｜しりょう
-資格｜しかく</t>
+資格｜しかく
+資本｜しほん
+資本主義｜しほんしゅぎ
+資本金｜しほんきん</t>
   </si>
   <si>
     <t>湿</t>
@@ -1137,6 +1149,7 @@
   </si>
   <si>
     <t>修理｜しゅうり
+修得｜しゅうとく
 研修｜けんしゅう
 必修｜ひっしゅう
 必修科目｜ひっしゅうかもく</t>
@@ -1146,7 +1159,8 @@
   </si>
   <si>
     <t>学習｜がくしゅう
-習慣｜しゅうかん</t>
+習慣｜しゅうかん
+習得｜しゅうとく</t>
   </si>
   <si>
     <t>秀</t>
@@ -1193,7 +1207,9 @@
   </si>
   <si>
     <t>修理｜しゅうり
-修復｜しゅうふく</t>
+修復｜しゅうふく
+修正｜しゅうせい
+修正案｜しゅうせいあん</t>
   </si>
   <si>
     <t>しょ</t>
@@ -1204,7 +1220,8 @@
   <si>
     <t>説明書｜せつめいしょ
 図書｜としょ
-書斎｜しょさい</t>
+書斎｜しょさい
+投書｜とうしょ</t>
   </si>
   <si>
     <t>処</t>
@@ -1355,6 +1372,7 @@
     <t>故障｜こしょう
 障害｜しょうがい
 障碍｜しょうがい
+障子｜しょうじ
 保障｜ほしょう</t>
   </si>
   <si>
@@ -1430,7 +1448,9 @@
   <si>
     <t>消火｜しょうか
 消化｜しょうか
-消火器｜しょうかき</t>
+消耗｜しょうもう
+消火器｜しょうかき
+消耗品｜しょうもうひん</t>
   </si>
   <si>
     <t>衝</t>
@@ -1602,7 +1622,8 @@
     <t>線</t>
   </si>
   <si>
-    <t>路線｜ろせん
+    <t>曲線｜きょくせん
+路線｜ろせん
 環状線｜かんじょうせん</t>
   </si>
   <si>
@@ -1632,7 +1653,8 @@
 即戦力｜そくせんりょく
 戦争｜せんそう
 戦略｜せんりゃく
-対戦｜たいせん</t>
+対戦｜たいせん
+戦前｜せんぜ</t>
   </si>
   <si>
     <t>跡</t>
@@ -1723,10 +1745,10 @@
 摂取量｜せっしゅりょう</t>
   </si>
   <si>
-    <t>践</t>
-  </si>
-  <si>
-    <t>実践｜じっせん</t>
+    <t>扇</t>
+  </si>
+  <si>
+    <t>扇子｜せんす</t>
   </si>
   <si>
     <t>折</t>
@@ -1740,6 +1762,12 @@
 折角｜せっかく</t>
   </si>
   <si>
+    <t>践</t>
+  </si>
+  <si>
+    <t>実践｜じっせん</t>
+  </si>
+  <si>
     <t>箋</t>
   </si>
   <si>
@@ -1752,7 +1780,9 @@
     <t>正解｜せいかい
 正確｜せいかく
 正式｜せいしき
-正常｜せいじょう</t>
+正常｜せいじょう
+修正｜しゅうせい
+修正案｜しゅうせいあん</t>
   </si>
   <si>
     <t>生鮮｜せいせん
@@ -2813,7 +2843,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2824,6 +2854,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3143,7 +3176,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3551,6 +3584,17 @@
       </c>
       <c r="C26" s="1" t="s">
         <v>81</v>
+      </c>
+    </row>
+    <row r="27" ht="36" spans="1:3">
+      <c r="A27" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -3594,1314 +3638,1314 @@
     </row>
     <row r="2" ht="72" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" ht="108" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" ht="90" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" ht="36" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" ht="54" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="6" ht="36" spans="1:9">
-      <c r="A6" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" ht="90" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" ht="93" customHeight="1" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" ht="72" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G9" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" ht="90" spans="1:9">
+      <c r="A10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="10" ht="72" spans="1:9">
-      <c r="A10" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" ht="72" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" ht="72" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" ht="73.2" customHeight="1" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" ht="36" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" ht="104.4" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" ht="40.8" customHeight="1" spans="1:7">
       <c r="A17" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" ht="108" spans="1:7">
       <c r="A18" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" ht="36" spans="1:7">
       <c r="A20" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="21" ht="72" spans="1:7">
       <c r="A21" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" ht="36" spans="1:7">
       <c r="A22" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" ht="36" spans="1:7">
       <c r="A23" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" ht="182.4" spans="1:7">
       <c r="A24" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25" ht="72" spans="1:7">
       <c r="A25" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" ht="36" spans="1:7">
       <c r="A26" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27" ht="54" spans="1:7">
       <c r="A27" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="28" ht="54" spans="1:7">
       <c r="A28" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="29" ht="36" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="30" ht="36" spans="1:7">
       <c r="A30" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="F31" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="32" ht="54" spans="1:7">
       <c r="A32" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="34" ht="36" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" ht="234" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38" ht="36" spans="1:3">
       <c r="A38" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="41" ht="36" spans="1:3">
       <c r="A41" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="43" ht="54" spans="1:3">
       <c r="A43" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="44" ht="54" spans="1:3">
       <c r="A44" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="46" ht="126" spans="1:3">
       <c r="A46" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="51" ht="52.2" customHeight="1" spans="1:3">
       <c r="A51" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="52" ht="54" spans="1:3">
       <c r="A52" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="53" ht="90" spans="1:3">
       <c r="A53" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="54" ht="180" spans="1:3">
       <c r="A54" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="55" ht="72" spans="1:3">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="55" ht="90" spans="1:3">
       <c r="A55" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="56" ht="36" spans="1:3">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="56" ht="54" spans="1:3">
       <c r="A56" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="57" ht="36" spans="1:3">
       <c r="A57" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="58" ht="36" spans="1:3">
       <c r="A58" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="59" ht="90" spans="1:3">
       <c r="A59" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="62" ht="36" spans="1:3">
       <c r="A62" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="63" ht="36" spans="1:3">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="63" ht="72" spans="1:3">
       <c r="A63" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="64" ht="54" spans="1:3">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="64" ht="72" spans="1:3">
       <c r="A64" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="65" ht="108" spans="1:3">
       <c r="A65" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="66" ht="36" spans="1:3">
       <c r="A66" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="67" ht="36" spans="1:3">
       <c r="A67" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="68" ht="90" spans="1:3">
       <c r="A68" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="69" ht="36" spans="1:3">
       <c r="A69" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="70" ht="36" spans="1:3">
       <c r="A70" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="72" ht="36" spans="1:3">
       <c r="A72" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="73" ht="54" spans="1:3">
       <c r="A73" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="74" ht="72" spans="1:3">
       <c r="A74" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="76" ht="72" spans="1:3">
       <c r="A76" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="78" ht="36" spans="1:3">
       <c r="A78" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="79" ht="72" spans="1:3">
       <c r="A79" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="82" ht="54" spans="1:3">
       <c r="A82" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="84" ht="72" spans="1:3">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="84" ht="90" spans="1:3">
       <c r="A84" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="85" ht="36" spans="1:3">
       <c r="A85" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="86" ht="36" spans="1:3">
       <c r="A86" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="87" ht="72" spans="1:3">
       <c r="A87" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="89" ht="90" spans="1:3">
       <c r="A89" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="92" ht="36" spans="1:3">
       <c r="A92" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="95" ht="54" spans="1:3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="95" ht="90" spans="1:3">
       <c r="A95" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -4932,170 +4976,170 @@
     </row>
     <row r="2" ht="18" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" ht="36" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D4" s="1"/>
     </row>
     <row r="5" ht="18" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6" ht="56.4" customHeight="1" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" ht="36" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" ht="78.6" customHeight="1" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10" ht="18.6" customHeight="1" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="12" ht="27.6" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C15" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="16" ht="15.6" spans="1:4">
       <c r="A16" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -5107,7 +5151,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -5139,431 +5183,442 @@
     </row>
     <row r="2" ht="67.2" customHeight="1" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="3" ht="36" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="4" ht="54" spans="1:7">
+      <c r="A4" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="4" ht="36" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>388</v>
-      </c>
       <c r="B4" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="5" ht="58.2" customHeight="1" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="6" ht="37.8" customHeight="1" spans="1:7">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="6" ht="108" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="7" ht="54" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8" ht="91.2" customHeight="1" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9" ht="126" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="10" ht="36" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="11" ht="57" customHeight="1" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="12" ht="108" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>428</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="14" ht="72" spans="1:7">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>431</v>
+        <v>390</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>308</v>
+        <v>433</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="15" ht="90" spans="1:7">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="15" ht="108" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="16" ht="180" spans="1:7">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="16" ht="90" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>434</v>
+        <v>291</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="17" ht="180" spans="1:3">
+      <c r="A17" s="1" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="1" t="s">
-        <v>431</v>
-      </c>
       <c r="B17" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="18" ht="36" spans="1:3">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="19" ht="36" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="20" ht="162" spans="1:3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="20" ht="36" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="21" ht="36" spans="1:3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="21" ht="162" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="22" ht="126" spans="1:3">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="22" ht="36" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="23" ht="126" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="24" ht="54" spans="1:3">
+        <v>450</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>452</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="25" ht="54" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="27" ht="36" spans="1:3">
+        <v>456</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="28" ht="54" spans="1:3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="28" ht="36" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="29" ht="54" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="30" ht="90" spans="1:3">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="30" ht="54" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="31" ht="36" spans="1:3">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="31" ht="90" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
+      </c>
+    </row>
+    <row r="32" ht="36" spans="1:3">
+      <c r="A32" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -5598,305 +5653,305 @@
     </row>
     <row r="2" ht="54" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="4" ht="54" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="5" ht="54" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6" ht="36" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="7" ht="130.2" customHeight="1" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="8" ht="144" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9" ht="36" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="10" ht="144" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="11" ht="72" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="13" ht="72" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
     <row r="16" ht="36.6" customHeight="1" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
     </row>
     <row r="18" ht="36" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="19" ht="36" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
   </sheetData>

--- a/漢字（かんじ）/s.xlsx
+++ b/漢字（かんじ）/s.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="1"/>
+    <workbookView windowWidth="18288" windowHeight="9180" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="さ" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="535">
   <si>
     <t>仮名</t>
   </si>
@@ -83,46 +83,34 @@
     <t>察</t>
   </si>
   <si>
-    <t>警察｜けいさつ</t>
-  </si>
-  <si>
-    <t>鎖</t>
-  </si>
-  <si>
-    <t>連鎖店｜れんさてん</t>
-  </si>
-  <si>
-    <t>擦</t>
-  </si>
-  <si>
-    <t>摩擦｜まさつ</t>
-  </si>
-  <si>
-    <t>作</t>
-  </si>
-  <si>
-    <t>動作｜どうさ</t>
-  </si>
-  <si>
-    <t>拶</t>
-  </si>
-  <si>
-    <t>挨拶｜あいさつ</t>
-  </si>
-  <si>
-    <t>査</t>
-  </si>
-  <si>
-    <t>検査｜けんさ
-調査｜ちょうさ　
+    <t>警察｜けいさつ
+考察｜こうさつ
 洞察｜どうさつ
 洞察力｜どうさつりょく</t>
   </si>
   <si>
-    <t>撮</t>
-  </si>
-  <si>
-    <t>撮影｜さつえい</t>
+    <t>鎖</t>
+  </si>
+  <si>
+    <t>連鎖店｜れんさてん</t>
+  </si>
+  <si>
+    <t>擦</t>
+  </si>
+  <si>
+    <t>摩擦｜まさつ</t>
+  </si>
+  <si>
+    <t>作</t>
+  </si>
+  <si>
+    <t>動作｜どうさ</t>
+  </si>
+  <si>
+    <t>拶</t>
+  </si>
+  <si>
+    <t>挨拶｜あいさつ</t>
   </si>
   <si>
     <t>さい</t>
@@ -136,7 +124,13 @@
 細胞｜さいぼう</t>
   </si>
   <si>
-    <t>冊</t>
+    <t>査</t>
+  </si>
+  <si>
+    <t>検査｜けんさつ
+調査｜ちょうさつ　
+考査｜こうさつ
+中間考査｜ちゅうかんこうさつ</t>
   </si>
   <si>
     <t>催</t>
@@ -146,16 +140,10 @@
 催涙｜さいるい</t>
   </si>
   <si>
-    <t>さく</t>
-  </si>
-  <si>
-    <t>策</t>
-  </si>
-  <si>
-    <t>政策｜せいさく
-対策｜たいさく
-対応策｜たいおうさく
-解決策｜かいけつさく</t>
+    <t>撮</t>
+  </si>
+  <si>
+    <t>撮影｜さつえい</t>
   </si>
   <si>
     <t>最</t>
@@ -171,6 +159,33 @@
 最小｜さいしょう</t>
   </si>
   <si>
+    <t>冊</t>
+  </si>
+  <si>
+    <t>際</t>
+  </si>
+  <si>
+    <t>国際｜こくさい</t>
+  </si>
+  <si>
+    <t>さく</t>
+  </si>
+  <si>
+    <t>策</t>
+  </si>
+  <si>
+    <t>政策｜せいさく
+対策｜たいさく
+対応策｜たいおうさく
+解決策｜かいけつさく</t>
+  </si>
+  <si>
+    <t>財</t>
+  </si>
+  <si>
+    <t>財布｜さいふ</t>
+  </si>
+  <si>
     <t>作文｜さくぶん
 作品｜さくひん
 制作｜せいさく
@@ -179,30 +194,6 @@
 創作｜そうさく</t>
   </si>
   <si>
-    <t>際</t>
-  </si>
-  <si>
-    <t>国際｜こくさい</t>
-  </si>
-  <si>
-    <t>錯</t>
-  </si>
-  <si>
-    <t>錯誤｜さくご</t>
-  </si>
-  <si>
-    <t>財</t>
-  </si>
-  <si>
-    <t>財布｜さいふ</t>
-  </si>
-  <si>
-    <t>索</t>
-  </si>
-  <si>
-    <t>探索｜たんさく</t>
-  </si>
-  <si>
     <t>裁</t>
   </si>
   <si>
@@ -210,10 +201,10 @@
 裁判｜さいばん</t>
   </si>
   <si>
-    <t>削</t>
-  </si>
-  <si>
-    <t>削除｜さくじょ</t>
+    <t>錯</t>
+  </si>
+  <si>
+    <t>錯誤｜さくご</t>
   </si>
   <si>
     <t>載</t>
@@ -222,6 +213,30 @@
     <t>記載｜きさい
 掲載｜けいさい
 連載｜れんさい</t>
+  </si>
+  <si>
+    <t>索</t>
+  </si>
+  <si>
+    <t>探索｜たんさく</t>
+  </si>
+  <si>
+    <t>菜</t>
+  </si>
+  <si>
+    <t>野菜｜やさい</t>
+  </si>
+  <si>
+    <t>削</t>
+  </si>
+  <si>
+    <t>削除｜さくじょ</t>
+  </si>
+  <si>
+    <t>彩</t>
+  </si>
+  <si>
+    <t>多彩｜たさい</t>
   </si>
   <si>
     <t>さき</t>
@@ -234,18 +249,6 @@
 連絡先｜れんらくさき
 先程｜さきほど
 行先｜ゆきさき</t>
-  </si>
-  <si>
-    <t>菜</t>
-  </si>
-  <si>
-    <t>野菜｜やさい</t>
-  </si>
-  <si>
-    <t>彩</t>
-  </si>
-  <si>
-    <t>多彩｜たさい</t>
   </si>
   <si>
     <t>災</t>
@@ -773,7 +776,8 @@
     <t>宿</t>
   </si>
   <si>
-    <t>宿泊｜しゅくはく</t>
+    <t>宿泊｜しゅくはく
+宿命｜しゅくめい</t>
   </si>
   <si>
     <t>肢</t>
@@ -1324,6 +1328,10 @@
     <t>奨</t>
   </si>
   <si>
+    <t>奨励｜しょうれい
+奨励金｜しょうれいきん</t>
+  </si>
+  <si>
     <t>正</t>
   </si>
   <si>
@@ -1921,6 +1929,9 @@
   <si>
     <t>声音｜せいおん
 声援｜せいえん</t>
+  </si>
+  <si>
+    <t>反省｜はんせい</t>
   </si>
   <si>
     <t>そ</t>
@@ -2853,10 +2864,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3176,13 +3187,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
     <col min="3" max="3" width="38.6666666666667" style="1" customWidth="1"/>
     <col min="4" max="6" width="8.88888888888889" style="1"/>
-    <col min="7" max="7" width="24.6666666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="33.3333333333333" style="1" customWidth="1"/>
     <col min="8" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
@@ -3242,7 +3253,7 @@
       <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -3286,29 +3297,29 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" ht="72" spans="1:7">
+    <row r="6" ht="59" customHeight="1" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" ht="54" spans="1:7">
+      <c r="G6" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" ht="36" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>27</v>
@@ -3322,90 +3333,90 @@
       <c r="F7" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="8" ht="72" spans="1:7">
+      <c r="G7" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" ht="144" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G8" s="2" t="s">
+    </row>
+    <row r="9" ht="72" spans="1:7">
+      <c r="A9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="9" ht="144" spans="1:7">
-      <c r="A9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="F9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" ht="108" spans="1:7">
+      <c r="A10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" ht="36" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12" ht="36" spans="1:7">
+    <row r="12" ht="54" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>46</v>
@@ -3414,7 +3425,7 @@
         <v>47</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>48</v>
@@ -3423,145 +3434,154 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" ht="74.4" customHeight="1" spans="1:7">
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>51</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G13" s="2" t="s">
+    </row>
+    <row r="14" ht="74.4" customHeight="1" spans="1:7">
+      <c r="A14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="15" ht="16.8" customHeight="1" spans="1:7">
+      <c r="F14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" ht="36" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="16" ht="16.8" customHeight="1" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="17" ht="21.6" customHeight="1" spans="1:3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" ht="16.8" customHeight="1" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" ht="16.8" customHeight="1" spans="1:3">
+        <v>63</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" ht="21.6" customHeight="1" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" ht="56.4" customHeight="1" spans="1:3">
+        <v>65</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" ht="16.8" customHeight="1" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" ht="56.4" customHeight="1" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>70</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" ht="36" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" ht="36" spans="1:3">
+        <v>72</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" ht="54" spans="1:3">
       <c r="A22" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="23" ht="54" spans="1:3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" ht="36" spans="1:3">
       <c r="A23" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="24" ht="36" spans="1:3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -3569,31 +3589,20 @@
         <v>69</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" ht="36" spans="1:3">
       <c r="A26" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="27" ht="36" spans="1:3">
-      <c r="A27" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B27" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C26" s="2" t="s">
         <v>83</v>
       </c>
     </row>
@@ -4075,7 +4084,7 @@
       <c r="F23" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="5" t="s">
         <v>179</v>
       </c>
     </row>
@@ -4123,7 +4132,7 @@
       <c r="A26" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>190</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -4731,12 +4740,15 @@
         <v>308</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" ht="36" spans="1:3">
       <c r="A77" s="1" t="s">
         <v>290</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>309</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="78" ht="36" spans="1:3">
@@ -4744,10 +4756,10 @@
         <v>290</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="79" ht="72" spans="1:3">
@@ -4755,10 +4767,10 @@
         <v>290</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -4766,10 +4778,10 @@
         <v>290</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -4777,10 +4789,10 @@
         <v>290</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="82" ht="54" spans="1:3">
@@ -4788,10 +4800,10 @@
         <v>290</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="83" spans="1:3">
@@ -4799,10 +4811,10 @@
         <v>290</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="84" ht="90" spans="1:3">
@@ -4810,10 +4822,10 @@
         <v>290</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="85" ht="36" spans="1:3">
@@ -4821,10 +4833,10 @@
         <v>290</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="86" ht="36" spans="1:3">
@@ -4832,10 +4844,10 @@
         <v>290</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="87" ht="72" spans="1:3">
@@ -4843,10 +4855,10 @@
         <v>290</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -4854,10 +4866,10 @@
         <v>290</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="89" ht="90" spans="1:3">
@@ -4865,10 +4877,10 @@
         <v>290</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -4876,10 +4888,10 @@
         <v>290</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -4887,10 +4899,10 @@
         <v>290</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="92" ht="36" spans="1:3">
@@ -4898,10 +4910,10 @@
         <v>290</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -4909,10 +4921,10 @@
         <v>290</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -4920,7 +4932,7 @@
         <v>290</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>250</v>
@@ -4931,10 +4943,10 @@
         <v>290</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -4942,10 +4954,10 @@
         <v>290</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -4976,167 +4988,167 @@
     </row>
     <row r="2" ht="18" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" ht="36" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D4" s="1"/>
     </row>
     <row r="5" ht="18" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" ht="56.4" customHeight="1" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8" ht="36" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" ht="78.6" customHeight="1" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" ht="18.6" customHeight="1" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="12" ht="27.6" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C15" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="16" ht="15.6" spans="1:4">
       <c r="A16" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>159</v>
@@ -5151,7 +5163,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -5183,384 +5195,384 @@
     </row>
     <row r="2" ht="67.2" customHeight="1" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="3" ht="36" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" ht="54" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5" ht="58.2" customHeight="1" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" ht="108" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" ht="54" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="8" ht="91.2" customHeight="1" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9" ht="126" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="10" ht="36" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="11" ht="57" customHeight="1" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12" ht="108" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="15" ht="108" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="16" ht="90" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>291</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="17" ht="180" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="19" ht="36" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="20" ht="36" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="21" ht="162" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="22" ht="36" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="23" ht="126" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="25" ht="54" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>160</v>
@@ -5568,57 +5580,68 @@
     </row>
     <row r="28" ht="36" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="29" ht="54" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="30" ht="54" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="31" ht="90" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="32" ht="36" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>470</v>
       </c>
     </row>
   </sheetData>
@@ -5653,305 +5676,305 @@
     </row>
     <row r="2" ht="54" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="4" ht="54" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="5" ht="54" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="6" ht="36" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="7" ht="130.2" customHeight="1" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="8" ht="144" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9" ht="36" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="10" ht="144" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="11" ht="72" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="13" ht="72" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="16" ht="36.6" customHeight="1" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="18" ht="36" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="19" ht="36" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
   </sheetData>

--- a/漢字（かんじ）/s.xlsx
+++ b/漢字（かんじ）/s.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="18288" windowHeight="9180" activeTab="3"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="さ" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="545">
   <si>
     <t>仮名</t>
   </si>
@@ -678,23 +678,24 @@
 植民｜しょくみん</t>
   </si>
   <si>
+    <t>私</t>
+  </si>
+  <si>
+    <t>私鉄｜してつ
+私人｜しじん</t>
+  </si>
+  <si>
+    <t>殖</t>
+  </si>
+  <si>
+    <t>生殖｜せいしょく</t>
+  </si>
+  <si>
     <t>師</t>
   </si>
   <si>
     <t>教師｜きょうし
 米津玄師｜よねづけんし</t>
-  </si>
-  <si>
-    <t>殖</t>
-  </si>
-  <si>
-    <t>生殖｜せいしょく</t>
-  </si>
-  <si>
-    <t>始</t>
-  </si>
-  <si>
-    <t>開始｜かいし</t>
   </si>
   <si>
     <t>職</t>
@@ -708,22 +709,22 @@
 職人技｜しょくにんわざ</t>
   </si>
   <si>
+    <t>始</t>
+  </si>
+  <si>
+    <t>開始｜かいし</t>
+  </si>
+  <si>
+    <t>色</t>
+  </si>
+  <si>
+    <t>特色｜とくしょく</t>
+  </si>
+  <si>
     <t>姿</t>
   </si>
   <si>
     <t>姿勢｜しせい</t>
-  </si>
-  <si>
-    <t>色</t>
-  </si>
-  <si>
-    <t>特色｜とくしょく</t>
-  </si>
-  <si>
-    <t>旨</t>
-  </si>
-  <si>
-    <t>要旨｜ようし</t>
   </si>
   <si>
     <t>触</t>
@@ -733,11 +734,10 @@
 接触不良｜せっしょくふりょう</t>
   </si>
   <si>
-    <t>刺</t>
-  </si>
-  <si>
-    <t>刺激｜しげき
-名刺｜めいし</t>
+    <t>旨</t>
+  </si>
+  <si>
+    <t>要旨｜ようし</t>
   </si>
   <si>
     <t>しゅく</t>
@@ -749,7 +749,22 @@
     <t>縮小｜しゅくしょう
 縮小版｜しゅくしょうばん
 萎縮｜いしゅく
-退縮｜たいしゅく</t>
+退縮｜たいしゅく
+圧縮｜あっしゅく</t>
+  </si>
+  <si>
+    <t>刺</t>
+  </si>
+  <si>
+    <t>刺激｜しげき
+名刺｜めいし</t>
+  </si>
+  <si>
+    <t>祝</t>
+  </si>
+  <si>
+    <t>祝日｜しゅくじつ
+祝賀｜しゅくが</t>
   </si>
   <si>
     <t>死</t>
@@ -759,11 +774,11 @@
 必死｜ひっし</t>
   </si>
   <si>
-    <t>祝</t>
-  </si>
-  <si>
-    <t>祝日｜しゅくじつ
-祝賀｜しゅくが</t>
+    <t>宿</t>
+  </si>
+  <si>
+    <t>宿泊｜しゅくはく
+宿命｜しゅくめい</t>
   </si>
   <si>
     <t>四</t>
@@ -771,19 +786,6 @@
   <si>
     <t>四肢｜しし
 四捨五入｜ししゃごにゅう</t>
-  </si>
-  <si>
-    <t>宿</t>
-  </si>
-  <si>
-    <t>宿泊｜しゅくはく
-宿命｜しゅくめい</t>
-  </si>
-  <si>
-    <t>肢</t>
-  </si>
-  <si>
-    <t>四肢｜しし</t>
   </si>
   <si>
     <t>しゅつ</t>
@@ -859,6 +861,22 @@
     </r>
   </si>
   <si>
+    <t>肢</t>
+  </si>
+  <si>
+    <t>四肢｜しし</t>
+  </si>
+  <si>
+    <t>しゅん</t>
+  </si>
+  <si>
+    <t>瞬</t>
+  </si>
+  <si>
+    <t>瞬間｜しゅんかん
+一瞬｜いっしゅん</t>
+  </si>
+  <si>
     <t>詞</t>
   </si>
   <si>
@@ -868,14 +886,10 @@
 形容動詞｜けいようどうし</t>
   </si>
   <si>
-    <t>しゅん</t>
-  </si>
-  <si>
-    <t>瞬</t>
-  </si>
-  <si>
-    <t>瞬間｜しゅんかん
-一瞬｜いっしゅん</t>
+    <t>竣</t>
+  </si>
+  <si>
+    <t>竣工｜しゅんこう</t>
   </si>
   <si>
     <t>子</t>
@@ -885,10 +899,13 @@
 少子化対策｜しょうしかたいさく</t>
   </si>
   <si>
-    <t>竣</t>
-  </si>
-  <si>
-    <t>竣工｜しゅんこう</t>
+    <t>しろ</t>
+  </si>
+  <si>
+    <t>白</t>
+  </si>
+  <si>
+    <t>面白｜おもしろ</t>
   </si>
   <si>
     <t>しん</t>
@@ -902,13 +919,7 @@
 申告書｜しんこくしょ</t>
   </si>
   <si>
-    <t>しろ</t>
-  </si>
-  <si>
-    <t>白</t>
-  </si>
-  <si>
-    <t>面白｜おもしろ</t>
+    <t>城</t>
   </si>
   <si>
     <t>親</t>
@@ -919,7 +930,10 @@
 親友｜しんゆう</t>
   </si>
   <si>
-    <t>城</t>
+    <t>しら</t>
+  </si>
+  <si>
+    <t>白髪｜しらが</t>
   </si>
   <si>
     <t>神</t>
@@ -929,10 +943,10 @@
 精神｜せいしん</t>
   </si>
   <si>
-    <t>しら</t>
-  </si>
-  <si>
-    <t>白髪｜しらが</t>
+    <t>しま</t>
+  </si>
+  <si>
+    <t>島</t>
   </si>
   <si>
     <t>真</t>
@@ -942,10 +956,7 @@
 真実｜しんじつ</t>
   </si>
   <si>
-    <t>しま</t>
-  </si>
-  <si>
-    <t>島</t>
+    <t>縞</t>
   </si>
   <si>
     <t>新</t>
@@ -954,7 +965,10 @@
     <t>新宿｜しんじゅく</t>
   </si>
   <si>
-    <t>縞</t>
+    <t>しるし</t>
+  </si>
+  <si>
+    <t>印</t>
   </si>
   <si>
     <t>信</t>
@@ -963,12 +977,6 @@
     <t>信じる｜しんじる
 信用｜しんよう
 信念｜しんねん</t>
-  </si>
-  <si>
-    <t>しるし</t>
-  </si>
-  <si>
-    <t>印</t>
   </si>
   <si>
     <t>心</t>
@@ -997,6 +1005,7 @@
 直進｜ちょくしん
 増進｜ぞうしん
 促進｜そくしん
+昇進｜しょうしん
 先進｜せんしん
 先進国｜せんしんこく
 促進効果｜そくしんこうか
@@ -1467,6 +1476,18 @@
     <t>衝突｜しょうとつ</t>
   </si>
   <si>
+    <t>傷</t>
+  </si>
+  <si>
+    <t>負傷｜ふしょう</t>
+  </si>
+  <si>
+    <t>昇</t>
+  </si>
+  <si>
+    <t>昇進｜しょうしん</t>
+  </si>
+  <si>
     <t>す</t>
   </si>
   <si>
@@ -1932,6 +1953,13 @@
   </si>
   <si>
     <t>反省｜はんせい</t>
+  </si>
+  <si>
+    <t>晴</t>
+  </si>
+  <si>
+    <t>晴天｜せいてん
+快晴｜かいせい</t>
   </si>
   <si>
     <t>そ</t>
@@ -2050,11 +2078,10 @@
     </r>
   </si>
   <si>
-    <t>側</t>
-  </si>
-  <si>
-    <t>外側｜がいそく
-内側｜ないそく</t>
+    <t>則</t>
+  </si>
+  <si>
+    <t>法則｜ほうそく</t>
   </si>
   <si>
     <t>そう</t>
@@ -2069,11 +2096,11 @@
 塗装｜とそう</t>
   </si>
   <si>
-    <t>測</t>
-  </si>
-  <si>
-    <t>測定｜そくてい
-測定値｜そくていち</t>
+    <t>側</t>
+  </si>
+  <si>
+    <t>外側｜がいそく
+内側｜ないそく</t>
   </si>
   <si>
     <t>送</t>
@@ -2089,6 +2116,20 @@
 送別｜そうべつ</t>
   </si>
   <si>
+    <t>測</t>
+  </si>
+  <si>
+    <t>測定｜そくてい
+測定値｜そくていち</t>
+  </si>
+  <si>
+    <t>早</t>
+  </si>
+  <si>
+    <t>早退｜そうたい
+遅刻早退｜ちこくそうたい</t>
+  </si>
+  <si>
     <t>速</t>
   </si>
   <si>
@@ -2097,16 +2138,6 @@
 速報｜そくほう
 速報版｜そくほうばん
 速達｜そくたつ</t>
-  </si>
-  <si>
-    <t>早</t>
-  </si>
-  <si>
-    <t>早退｜そうたい
-遅刻早退｜ちこくそうたい</t>
-  </si>
-  <si>
-    <t>促成｜そくせい</t>
   </si>
   <si>
     <t>相当｜そうとう
@@ -2119,10 +2150,7 @@
 相談室｜そうだんしつ</t>
   </si>
   <si>
-    <t>即</t>
-  </si>
-  <si>
-    <t>即戦力｜そくせんりょく</t>
+    <t>促成｜そくせい</t>
   </si>
   <si>
     <t>想</t>
@@ -2134,24 +2162,24 @@
 想像力｜そうぞうりょく</t>
   </si>
   <si>
+    <t>即</t>
+  </si>
+  <si>
+    <t>即戦力｜そくせんりょく</t>
+  </si>
+  <si>
+    <t>操</t>
+  </si>
+  <si>
+    <t>操作｜そうさく</t>
+  </si>
+  <si>
     <t>息</t>
   </si>
   <si>
     <t>利息｜りそく
 休息｜きゅうそく
 貯金利息｜ちょきんりそく</t>
-  </si>
-  <si>
-    <t>操</t>
-  </si>
-  <si>
-    <t>操作｜そうさく</t>
-  </si>
-  <si>
-    <t>そこ</t>
-  </si>
-  <si>
-    <t>底</t>
   </si>
   <si>
     <t>創</t>
@@ -2163,6 +2191,18 @@
 創設｜そうせつ</t>
   </si>
   <si>
+    <t>そこ</t>
+  </si>
+  <si>
+    <t>底</t>
+  </si>
+  <si>
+    <t>捜</t>
+  </si>
+  <si>
+    <t>捜索｜そうさく</t>
+  </si>
+  <si>
     <t>そで</t>
   </si>
   <si>
@@ -2170,12 +2210,6 @@
   </si>
   <si>
     <t>半袖｜はんそで</t>
-  </si>
-  <si>
-    <t>捜</t>
-  </si>
-  <si>
-    <t>捜索｜そうさく</t>
   </si>
   <si>
     <t>倉</t>
@@ -2854,7 +2888,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2864,9 +2898,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -3615,7 +3646,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I96"/>
+  <dimension ref="A1:I99"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3975,7 +4006,7 @@
       <c r="B18" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>156</v>
       </c>
       <c r="E18" s="1" t="s">
@@ -3995,7 +4026,7 @@
       <c r="B19" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>160</v>
       </c>
       <c r="E19" s="1" t="s">
@@ -4028,7 +4059,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="21" ht="72" spans="1:7">
+    <row r="21" ht="90" spans="1:7">
       <c r="A21" s="1" t="s">
         <v>84</v>
       </c>
@@ -4084,7 +4115,7 @@
       <c r="F23" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="G23" s="2" t="s">
         <v>179</v>
       </c>
     </row>
@@ -4108,7 +4139,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="25" ht="72" spans="1:7">
+    <row r="25" ht="36" spans="1:7">
       <c r="A25" s="1" t="s">
         <v>84</v>
       </c>
@@ -4128,11 +4159,11 @@
         <v>189</v>
       </c>
     </row>
-    <row r="26" ht="36" spans="1:7">
+    <row r="26" ht="72" spans="1:7">
       <c r="A26" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="1" t="s">
         <v>190</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -4148,29 +4179,29 @@
         <v>193</v>
       </c>
     </row>
-    <row r="27" ht="54" spans="1:7">
+    <row r="27" ht="36" spans="1:7">
       <c r="A27" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C27" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="E27" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F27" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="G27" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="28" ht="54" spans="1:7">
       <c r="A28" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>200</v>
@@ -4179,15 +4210,15 @@
         <v>201</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="29" ht="36" spans="1:7">
+    <row r="29" ht="54" spans="1:7">
       <c r="A29" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>203</v>
@@ -4199,7 +4230,7 @@
         <v>205</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>206</v>
@@ -4207,7 +4238,7 @@
     </row>
     <row r="30" ht="36" spans="1:7">
       <c r="A30" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>207</v>
@@ -4222,14 +4253,14 @@
         <v>210</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" ht="36" spans="1:7">
       <c r="A31" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="2" t="s">
         <v>212</v>
       </c>
       <c r="E31" s="1" t="s">
@@ -4239,14 +4270,14 @@
         <v>213</v>
       </c>
     </row>
-    <row r="32" ht="54" spans="1:7">
+    <row r="32" spans="1:7">
       <c r="A32" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>215</v>
       </c>
       <c r="E32" s="1" t="s">
@@ -4256,9 +4287,9 @@
         <v>217</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" ht="54" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>218</v>
@@ -4267,9 +4298,9 @@
         <v>219</v>
       </c>
     </row>
-    <row r="34" ht="36" spans="1:3">
+    <row r="34" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>220</v>
@@ -4278,64 +4309,64 @@
         <v>221</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" ht="36" spans="1:3">
       <c r="A35" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="2" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="36" ht="234" spans="1:3">
+    <row r="36" spans="1:3">
       <c r="A36" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="1" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" ht="252" spans="1:3">
       <c r="A37" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B37" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="38" ht="36" spans="1:3">
+    <row r="38" spans="1:3">
       <c r="A38" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B38" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="1" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" ht="36" spans="1:3">
       <c r="A39" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="2" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>232</v>
@@ -4344,42 +4375,42 @@
         <v>233</v>
       </c>
     </row>
-    <row r="41" ht="36" spans="1:3">
+    <row r="41" spans="1:3">
       <c r="A41" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" ht="36" spans="1:3">
       <c r="A42" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="C42" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C42" s="1" t="s">
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="1" t="s">
         <v>238</v>
-      </c>
-    </row>
-    <row r="43" ht="54" spans="1:3">
-      <c r="A43" s="1" t="s">
-        <v>236</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="1" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="44" ht="54" spans="1:3">
       <c r="A44" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>241</v>
@@ -4388,31 +4419,31 @@
         <v>242</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" ht="54" spans="1:3">
       <c r="A45" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="2" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="46" ht="126" spans="1:3">
+    <row r="46" spans="1:3">
       <c r="A46" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" ht="126" spans="1:3">
       <c r="A47" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>247</v>
@@ -4423,7 +4454,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>249</v>
@@ -4434,7 +4465,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>251</v>
@@ -4445,7 +4476,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>253</v>
@@ -4456,18 +4487,18 @@
     </row>
     <row r="51" ht="52.2" customHeight="1" spans="1:3">
       <c r="A51" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="C51" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C51" s="2" t="s">
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="1" t="s">
         <v>257</v>
-      </c>
-    </row>
-    <row r="52" ht="54" spans="1:3">
-      <c r="A52" s="1" t="s">
-        <v>255</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>258</v>
@@ -4476,9 +4507,9 @@
         <v>259</v>
       </c>
     </row>
-    <row r="53" ht="90" spans="1:3">
+    <row r="53" ht="54" spans="1:3">
       <c r="A53" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>260</v>
@@ -4487,9 +4518,9 @@
         <v>261</v>
       </c>
     </row>
-    <row r="54" ht="180" spans="1:3">
+    <row r="54" ht="90" spans="1:3">
       <c r="A54" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>262</v>
@@ -4498,9 +4529,9 @@
         <v>263</v>
       </c>
     </row>
-    <row r="55" ht="90" spans="1:3">
+    <row r="55" ht="180" spans="1:3">
       <c r="A55" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>264</v>
@@ -4509,9 +4540,9 @@
         <v>265</v>
       </c>
     </row>
-    <row r="56" ht="54" spans="1:3">
+    <row r="56" ht="90" spans="1:3">
       <c r="A56" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>266</v>
@@ -4520,9 +4551,9 @@
         <v>267</v>
       </c>
     </row>
-    <row r="57" ht="36" spans="1:3">
+    <row r="57" ht="54" spans="1:3">
       <c r="A57" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>268</v>
@@ -4533,7 +4564,7 @@
     </row>
     <row r="58" ht="36" spans="1:3">
       <c r="A58" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>270</v>
@@ -4542,9 +4573,9 @@
         <v>271</v>
       </c>
     </row>
-    <row r="59" ht="90" spans="1:3">
+    <row r="59" ht="36" spans="1:3">
       <c r="A59" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>272</v>
@@ -4553,31 +4584,31 @@
         <v>273</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" ht="90" spans="1:3">
       <c r="A60" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="2" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="1" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="62" ht="36" spans="1:3">
+    <row r="62" spans="1:3">
       <c r="A62" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>278</v>
@@ -4586,31 +4617,31 @@
         <v>279</v>
       </c>
     </row>
-    <row r="63" ht="72" spans="1:3">
+    <row r="63" ht="36" spans="1:3">
       <c r="A63" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="64" ht="72" spans="1:3">
       <c r="A64" s="1" t="s">
-        <v>281</v>
+        <v>257</v>
       </c>
       <c r="B64" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="C64" s="2" t="s">
+    </row>
+    <row r="65" ht="72" spans="1:3">
+      <c r="A65" s="1" t="s">
         <v>283</v>
-      </c>
-    </row>
-    <row r="65" ht="108" spans="1:3">
-      <c r="A65" s="1" t="s">
-        <v>281</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>284</v>
@@ -4619,9 +4650,9 @@
         <v>285</v>
       </c>
     </row>
-    <row r="66" ht="36" spans="1:3">
+    <row r="66" ht="108" spans="1:3">
       <c r="A66" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>286</v>
@@ -4632,7 +4663,7 @@
     </row>
     <row r="67" ht="36" spans="1:3">
       <c r="A67" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>288</v>
@@ -4641,20 +4672,20 @@
         <v>289</v>
       </c>
     </row>
-    <row r="68" ht="90" spans="1:3">
+    <row r="68" ht="36" spans="1:3">
       <c r="A68" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="C68" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C68" s="2" t="s">
+    </row>
+    <row r="69" ht="90" spans="1:3">
+      <c r="A69" s="1" t="s">
         <v>292</v>
-      </c>
-    </row>
-    <row r="69" ht="36" spans="1:3">
-      <c r="A69" s="1" t="s">
-        <v>290</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>293</v>
@@ -4665,7 +4696,7 @@
     </row>
     <row r="70" ht="36" spans="1:3">
       <c r="A70" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>295</v>
@@ -4674,31 +4705,31 @@
         <v>296</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
+    <row r="71" ht="36" spans="1:3">
       <c r="A71" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" s="2" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="72" ht="36" spans="1:3">
+    <row r="72" spans="1:3">
       <c r="A72" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="1" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="73" ht="54" spans="1:3">
+    <row r="73" ht="36" spans="1:3">
       <c r="A73" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>301</v>
@@ -4707,9 +4738,9 @@
         <v>302</v>
       </c>
     </row>
-    <row r="74" ht="72" spans="1:3">
+    <row r="74" ht="54" spans="1:3">
       <c r="A74" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>303</v>
@@ -4718,42 +4749,42 @@
         <v>304</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" ht="72" spans="1:3">
       <c r="A75" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="2" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="76" ht="72" spans="1:3">
+    <row r="76" spans="1:3">
       <c r="A76" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C76" s="1" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="77" ht="36" spans="1:3">
+    <row r="77" ht="72" spans="1:3">
       <c r="A77" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C77" s="5" t="s">
+      <c r="C77" s="2" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="78" ht="36" spans="1:3">
       <c r="A78" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>311</v>
@@ -4762,9 +4793,9 @@
         <v>312</v>
       </c>
     </row>
-    <row r="79" ht="72" spans="1:3">
+    <row r="79" ht="36" spans="1:3">
       <c r="A79" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>313</v>
@@ -4773,20 +4804,20 @@
         <v>314</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" ht="72" spans="1:3">
       <c r="A80" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="2" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>317</v>
@@ -4795,42 +4826,42 @@
         <v>318</v>
       </c>
     </row>
-    <row r="82" ht="54" spans="1:3">
+    <row r="82" spans="1:3">
       <c r="A82" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" s="1" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" ht="54" spans="1:3">
       <c r="A83" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C83" s="2" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="84" ht="90" spans="1:3">
+    <row r="84" spans="1:3">
       <c r="A84" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C84" s="1" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="85" ht="36" spans="1:3">
+    <row r="85" ht="90" spans="1:3">
       <c r="A85" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>325</v>
@@ -4841,7 +4872,7 @@
     </row>
     <row r="86" ht="36" spans="1:3">
       <c r="A86" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>327</v>
@@ -4850,9 +4881,9 @@
         <v>328</v>
       </c>
     </row>
-    <row r="87" ht="72" spans="1:3">
+    <row r="87" ht="36" spans="1:3">
       <c r="A87" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>329</v>
@@ -4861,42 +4892,42 @@
         <v>330</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" ht="72" spans="1:3">
       <c r="A88" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C88" s="2" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="89" ht="90" spans="1:3">
+    <row r="89" spans="1:3">
       <c r="A89" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="C89" s="1" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" ht="90" spans="1:3">
       <c r="A90" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C90" s="2" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>337</v>
@@ -4905,59 +4936,92 @@
         <v>338</v>
       </c>
     </row>
-    <row r="92" ht="36" spans="1:3">
+    <row r="92" spans="1:3">
       <c r="A92" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" s="1" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" ht="36" spans="1:3">
       <c r="A93" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C93" s="2" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>343</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="95" ht="90" spans="1:3">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
       <c r="A95" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="C95" s="2" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="96" spans="1:3">
+      <c r="C95" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="96" ht="90" spans="1:3">
       <c r="A96" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C96" s="2" t="s">
         <v>347</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>353</v>
       </c>
     </row>
   </sheetData>
@@ -4988,170 +5052,170 @@
     </row>
     <row r="2" ht="18" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" ht="36" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="D4" s="1"/>
     </row>
     <row r="5" ht="18" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" ht="56.4" customHeight="1" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8" ht="36" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9" ht="78.6" customHeight="1" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10" ht="18.6" customHeight="1" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C11" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="12" ht="27.6" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="C15" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="16" ht="15.6" spans="1:4">
       <c r="A16" s="4" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -5163,7 +5227,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -5195,453 +5259,464 @@
     </row>
     <row r="2" ht="67.2" customHeight="1" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="3" ht="36" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4" ht="54" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="5" ht="58.2" customHeight="1" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="6" ht="108" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="7" ht="54" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="8" ht="91.2" customHeight="1" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9" ht="126" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10" ht="36" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="11" ht="57" customHeight="1" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
     </row>
     <row r="12" ht="108" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
     </row>
     <row r="15" ht="108" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
     </row>
     <row r="16" ht="90" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="17" ht="180" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="19" ht="36" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="20" ht="36" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
     </row>
     <row r="21" ht="162" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
     </row>
     <row r="22" ht="36" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="23" ht="126" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="25" ht="54" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" ht="36" spans="1:3">
       <c r="A28" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="29" ht="54" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="30" ht="54" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="31" ht="90" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="32" ht="36" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>470</v>
+        <v>476</v>
+      </c>
+    </row>
+    <row r="34" ht="36" spans="1:3">
+      <c r="A34" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>478</v>
       </c>
     </row>
   </sheetData>
@@ -5676,305 +5751,314 @@
     </row>
     <row r="2" ht="54" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
     </row>
     <row r="4" ht="54" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="5" ht="54" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
     </row>
     <row r="6" ht="36" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>493</v>
+        <v>500</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="7" ht="130.2" customHeight="1" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
     </row>
     <row r="8" ht="144" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="G8" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="9" ht="90" spans="1:7">
+      <c r="A9" s="1" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="9" ht="36" spans="1:7">
-      <c r="A9" s="1" t="s">
-        <v>494</v>
-      </c>
       <c r="B9" s="1" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>505</v>
+        <v>513</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="10" ht="144" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
     </row>
     <row r="11" ht="72" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>519</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="12" ht="54" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>515</v>
+        <v>492</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>516</v>
+        <v>523</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="13" ht="72" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>523</v>
+        <v>530</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>524</v>
+        <v>534</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>525</v>
+        <v>535</v>
       </c>
     </row>
     <row r="16" ht="36.6" customHeight="1" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
     </row>
     <row r="18" ht="36" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
     </row>
     <row r="19" ht="36" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>534</v>
+        <v>544</v>
       </c>
     </row>
   </sheetData>

--- a/漢字（かんじ）/s.xlsx
+++ b/漢字（かんじ）/s.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="さ" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="547">
   <si>
     <t>仮名</t>
   </si>
@@ -346,6 +346,7 @@
   <si>
     <t>幻視｜げんし
 無視｜むし
+軽視｜けいし
 視聴｜しちょう
 視野｜しや</t>
   </si>
@@ -1454,7 +1455,9 @@
     <t>将</t>
   </si>
   <si>
-    <t>将来｜しょうらい</t>
+    <t>将来｜しょうらい
+将棋｜しょうぎ
+王将｜おうしょう</t>
   </si>
   <si>
     <t>相</t>
@@ -1801,6 +1804,12 @@
   </si>
   <si>
     <t>処方箋｜しょほうせん</t>
+  </si>
+  <si>
+    <t>繊</t>
+  </si>
+  <si>
+    <t>繊維｜せんい</t>
   </si>
   <si>
     <t>せい</t>
@@ -2888,7 +2897,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2899,6 +2908,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3676,7 +3688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="72" spans="1:9">
+    <row r="2" ht="90" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>84</v>
       </c>
@@ -4958,14 +4970,14 @@
         <v>342</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" ht="54" spans="1:3">
       <c r="A94" s="1" t="s">
         <v>292</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C94" s="6" t="s">
         <v>344</v>
       </c>
     </row>
@@ -5227,7 +5239,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -5499,42 +5511,42 @@
         <v>441</v>
       </c>
     </row>
-    <row r="15" ht="108" spans="1:7">
+    <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="16" ht="108" spans="1:7">
+      <c r="A16" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="16" ht="90" spans="1:7">
-      <c r="A16" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="17" ht="90" spans="1:3">
+      <c r="A17" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="17" ht="180" spans="1:3">
-      <c r="A17" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>445</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" ht="180" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>447</v>
@@ -5543,9 +5555,9 @@
         <v>448</v>
       </c>
     </row>
-    <row r="19" ht="36" spans="1:3">
+    <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>449</v>
@@ -5556,7 +5568,7 @@
     </row>
     <row r="20" ht="36" spans="1:3">
       <c r="A20" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>451</v>
@@ -5565,9 +5577,9 @@
         <v>452</v>
       </c>
     </row>
-    <row r="21" ht="162" spans="1:3">
+    <row r="21" ht="36" spans="1:3">
       <c r="A21" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>453</v>
@@ -5576,9 +5588,9 @@
         <v>454</v>
       </c>
     </row>
-    <row r="22" ht="36" spans="1:3">
+    <row r="22" ht="162" spans="1:3">
       <c r="A22" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>455</v>
@@ -5587,9 +5599,9 @@
         <v>456</v>
       </c>
     </row>
-    <row r="23" ht="126" spans="1:3">
+    <row r="23" ht="36" spans="1:3">
       <c r="A23" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>457</v>
@@ -5598,64 +5610,64 @@
         <v>458</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" ht="126" spans="1:3">
       <c r="A24" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="2" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="25" ht="54" spans="1:3">
+    <row r="25" spans="1:3">
       <c r="A25" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" ht="54" spans="1:3">
       <c r="A26" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="2" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="28" ht="36" spans="1:3">
-      <c r="A28" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="29" ht="54" spans="1:3">
+    <row r="29" ht="36" spans="1:3">
       <c r="A29" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>468</v>
@@ -5666,7 +5678,7 @@
     </row>
     <row r="30" ht="54" spans="1:3">
       <c r="A30" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>470</v>
@@ -5675,9 +5687,9 @@
         <v>471</v>
       </c>
     </row>
-    <row r="31" ht="90" spans="1:3">
+    <row r="31" ht="54" spans="1:3">
       <c r="A31" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>472</v>
@@ -5686,9 +5698,9 @@
         <v>473</v>
       </c>
     </row>
-    <row r="32" ht="36" spans="1:3">
+    <row r="32" ht="90" spans="1:3">
       <c r="A32" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>474</v>
@@ -5697,26 +5709,37 @@
         <v>475</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" ht="36" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="34" ht="36" spans="1:3">
-      <c r="A34" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>478</v>
+      </c>
+    </row>
+    <row r="35" ht="36" spans="1:3">
+      <c r="A35" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -5751,314 +5774,314 @@
     </row>
     <row r="2" ht="54" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="4" ht="54" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="5" ht="54" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>356</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="6" ht="36" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="7" ht="130.2" customHeight="1" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="8" ht="144" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="9" ht="90" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="10" ht="144" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>345</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="11" ht="72" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="12" ht="54" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="13" ht="72" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="16" ht="36.6" customHeight="1" spans="1:7">
       <c r="A16" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="18" ht="36" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="19" ht="36" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
   </sheetData>

--- a/漢字（かんじ）/s.xlsx
+++ b/漢字（かんじ）/s.xlsx
@@ -1752,7 +1752,9 @@
     <t>宣</t>
   </si>
   <si>
-    <t>宣伝費｜せんでんひ
+    <t>宣伝｜せんでん
+宣伝費｜せんでんひ
+宣伝活動｜せんでんかつどう
 宣言｜せんげん</t>
   </si>
   <si>
@@ -2897,7 +2899,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2908,9 +2910,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4977,7 +4976,7 @@
       <c r="B94" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C94" s="6" t="s">
+      <c r="C94" s="2" t="s">
         <v>344</v>
       </c>
     </row>
@@ -5429,7 +5428,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="10" ht="36" spans="1:7">
+    <row r="10" ht="72" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>397</v>
       </c>
